--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>136583233</v>
       </c>
       <c r="B5" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136583235</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136583240</v>
       </c>
       <c r="B9" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136583223</v>
       </c>
       <c r="B24" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136583225</v>
       </c>
       <c r="B25" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>136583227</v>
       </c>
       <c r="B26" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136583232</v>
       </c>
       <c r="B27" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>136583236</v>
       </c>
       <c r="B28" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136583239</v>
       </c>
       <c r="B29" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136583243</v>
       </c>
       <c r="B30" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>136583233</v>
       </c>
       <c r="B5" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136583235</v>
       </c>
       <c r="B6" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136583240</v>
       </c>
       <c r="B9" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136583223</v>
       </c>
       <c r="B24" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136583225</v>
       </c>
       <c r="B25" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>136583227</v>
       </c>
       <c r="B26" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136583232</v>
       </c>
       <c r="B27" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>136583236</v>
       </c>
       <c r="B28" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136583239</v>
       </c>
       <c r="B29" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136583243</v>
       </c>
       <c r="B30" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>136583233</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136583235</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136583240</v>
       </c>
       <c r="B9" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136583213</v>
       </c>
       <c r="B10" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136583218</v>
       </c>
       <c r="B11" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136583226</v>
       </c>
       <c r="B12" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136583238</v>
       </c>
       <c r="B13" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136583248</v>
       </c>
       <c r="B14" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136583249</v>
       </c>
       <c r="B15" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>136583250</v>
       </c>
       <c r="B16" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>136583251</v>
       </c>
       <c r="B17" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>136583252</v>
       </c>
       <c r="B18" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>136583253</v>
       </c>
       <c r="B19" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136583254</v>
       </c>
       <c r="B20" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136583223</v>
       </c>
       <c r="B24" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136583225</v>
       </c>
       <c r="B25" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>136583227</v>
       </c>
       <c r="B26" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136583232</v>
       </c>
       <c r="B27" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>136583236</v>
       </c>
       <c r="B28" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136583239</v>
       </c>
       <c r="B29" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136583243</v>
       </c>
       <c r="B30" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136583220</v>
       </c>
       <c r="B31" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>136583229</v>
       </c>
       <c r="B32" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136583230</v>
       </c>
       <c r="B33" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>136583242</v>
       </c>
       <c r="B37" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>136583231</v>
       </c>
       <c r="B51" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>136583247</v>
       </c>
       <c r="B52" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>136583233</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136583235</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136583240</v>
       </c>
       <c r="B9" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136583223</v>
       </c>
       <c r="B24" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136583225</v>
       </c>
       <c r="B25" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>136583227</v>
       </c>
       <c r="B26" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136583232</v>
       </c>
       <c r="B27" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>136583236</v>
       </c>
       <c r="B28" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136583239</v>
       </c>
       <c r="B29" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136583243</v>
       </c>
       <c r="B30" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>136583233</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136583235</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136583240</v>
       </c>
       <c r="B9" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136583213</v>
       </c>
       <c r="B10" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136583218</v>
       </c>
       <c r="B11" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136583226</v>
       </c>
       <c r="B12" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136583238</v>
       </c>
       <c r="B13" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136583248</v>
       </c>
       <c r="B14" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136583249</v>
       </c>
       <c r="B15" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>136583250</v>
       </c>
       <c r="B16" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>136583251</v>
       </c>
       <c r="B17" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>136583252</v>
       </c>
       <c r="B18" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>136583253</v>
       </c>
       <c r="B19" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136583254</v>
       </c>
       <c r="B20" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136583223</v>
       </c>
       <c r="B24" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136583225</v>
       </c>
       <c r="B25" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>136583227</v>
       </c>
       <c r="B26" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136583232</v>
       </c>
       <c r="B27" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>136583236</v>
       </c>
       <c r="B28" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136583239</v>
       </c>
       <c r="B29" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136583243</v>
       </c>
       <c r="B30" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136583220</v>
       </c>
       <c r="B31" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>136583229</v>
       </c>
       <c r="B32" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136583230</v>
       </c>
       <c r="B33" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>136583242</v>
       </c>
       <c r="B37" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>136583233</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136583235</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136583240</v>
       </c>
       <c r="B9" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136583213</v>
       </c>
       <c r="B10" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136583218</v>
       </c>
       <c r="B11" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136583226</v>
       </c>
       <c r="B12" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136583238</v>
       </c>
       <c r="B13" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136583248</v>
       </c>
       <c r="B14" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136583249</v>
       </c>
       <c r="B15" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>136583250</v>
       </c>
       <c r="B16" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>136583251</v>
       </c>
       <c r="B17" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>136583252</v>
       </c>
       <c r="B18" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>136583253</v>
       </c>
       <c r="B19" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136583254</v>
       </c>
       <c r="B20" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136583223</v>
       </c>
       <c r="B24" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136583225</v>
       </c>
       <c r="B25" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>136583227</v>
       </c>
       <c r="B26" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136583232</v>
       </c>
       <c r="B27" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>136583236</v>
       </c>
       <c r="B28" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136583239</v>
       </c>
       <c r="B29" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136583243</v>
       </c>
       <c r="B30" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136583220</v>
       </c>
       <c r="B31" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>136583229</v>
       </c>
       <c r="B32" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136583230</v>
       </c>
       <c r="B33" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>136583242</v>
       </c>
       <c r="B37" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>136583233</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136583235</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136583240</v>
       </c>
       <c r="B9" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136583213</v>
       </c>
       <c r="B10" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136583218</v>
       </c>
       <c r="B11" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136583226</v>
       </c>
       <c r="B12" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136583238</v>
       </c>
       <c r="B13" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136583248</v>
       </c>
       <c r="B14" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136583249</v>
       </c>
       <c r="B15" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>136583250</v>
       </c>
       <c r="B16" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>136583251</v>
       </c>
       <c r="B17" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>136583252</v>
       </c>
       <c r="B18" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>136583253</v>
       </c>
       <c r="B19" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136583254</v>
       </c>
       <c r="B20" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136583223</v>
       </c>
       <c r="B24" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136583225</v>
       </c>
       <c r="B25" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>136583227</v>
       </c>
       <c r="B26" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136583232</v>
       </c>
       <c r="B27" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>136583236</v>
       </c>
       <c r="B28" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136583239</v>
       </c>
       <c r="B29" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136583243</v>
       </c>
       <c r="B30" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136583220</v>
       </c>
       <c r="B31" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>136583229</v>
       </c>
       <c r="B32" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136583230</v>
       </c>
       <c r="B33" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>136583242</v>
       </c>
       <c r="B37" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>136583233</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136583235</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136583240</v>
       </c>
       <c r="B9" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136583223</v>
       </c>
       <c r="B24" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136583225</v>
       </c>
       <c r="B25" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>136583227</v>
       </c>
       <c r="B26" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136583232</v>
       </c>
       <c r="B27" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>136583236</v>
       </c>
       <c r="B28" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136583239</v>
       </c>
       <c r="B29" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136583243</v>
       </c>
       <c r="B30" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>136583233</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136583235</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136583240</v>
       </c>
       <c r="B9" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136583213</v>
       </c>
       <c r="B10" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136583218</v>
       </c>
       <c r="B11" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136583226</v>
       </c>
       <c r="B12" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136583238</v>
       </c>
       <c r="B13" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136583248</v>
       </c>
       <c r="B14" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136583249</v>
       </c>
       <c r="B15" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>136583250</v>
       </c>
       <c r="B16" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>136583251</v>
       </c>
       <c r="B17" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>136583252</v>
       </c>
       <c r="B18" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>136583253</v>
       </c>
       <c r="B19" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136583254</v>
       </c>
       <c r="B20" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136583223</v>
       </c>
       <c r="B24" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136583225</v>
       </c>
       <c r="B25" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>136583227</v>
       </c>
       <c r="B26" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136583232</v>
       </c>
       <c r="B27" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>136583236</v>
       </c>
       <c r="B28" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136583239</v>
       </c>
       <c r="B29" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136583243</v>
       </c>
       <c r="B30" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136583220</v>
       </c>
       <c r="B31" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>136583229</v>
       </c>
       <c r="B32" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136583230</v>
       </c>
       <c r="B33" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>136583242</v>
       </c>
       <c r="B37" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>136583233</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136583235</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136583240</v>
       </c>
       <c r="B9" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136583213</v>
       </c>
       <c r="B10" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136583218</v>
       </c>
       <c r="B11" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136583226</v>
       </c>
       <c r="B12" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136583238</v>
       </c>
       <c r="B13" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>136583248</v>
       </c>
       <c r="B14" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136583249</v>
       </c>
       <c r="B15" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>136583250</v>
       </c>
       <c r="B16" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>136583251</v>
       </c>
       <c r="B17" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>136583252</v>
       </c>
       <c r="B18" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>136583253</v>
       </c>
       <c r="B19" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136583254</v>
       </c>
       <c r="B20" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136583223</v>
       </c>
       <c r="B24" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136583225</v>
       </c>
       <c r="B25" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>136583227</v>
       </c>
       <c r="B26" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136583232</v>
       </c>
       <c r="B27" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>136583236</v>
       </c>
       <c r="B28" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136583239</v>
       </c>
       <c r="B29" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>136583243</v>
       </c>
       <c r="B30" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136583220</v>
       </c>
       <c r="B31" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>136583229</v>
       </c>
       <c r="B32" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136583230</v>
       </c>
       <c r="B33" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>136583242</v>
       </c>
       <c r="B37" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136583212</v>
       </c>
       <c r="B57" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>136583215</v>
       </c>
       <c r="B58" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136583216</v>
       </c>
       <c r="B59" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>136583217</v>
       </c>
       <c r="B60" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>136583222</v>
       </c>
       <c r="B61" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>136583224</v>
       </c>
       <c r="B62" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ73"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134833902</v>
+        <v>137454525</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730791</v>
+        <v>730884</v>
       </c>
       <c r="R2" t="n">
-        <v>7156182</v>
+        <v>7155941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:08</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,28 +770,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833902</t>
+          <t>https://artportalen.se/Sighting/137454525</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134833920</v>
+        <v>134833902</v>
       </c>
       <c r="B3" t="n">
         <v>92088</v>
@@ -831,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730902</v>
+        <v>730791</v>
       </c>
       <c r="R3" t="n">
-        <v>7155804</v>
+        <v>7156182</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,13 +897,13 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833920</t>
+          <t>https://artportalen.se/Sighting/134833902</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134833922</v>
+        <v>134833920</v>
       </c>
       <c r="B4" t="n">
         <v>92088</v>
@@ -947,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730864</v>
+        <v>730902</v>
       </c>
       <c r="R4" t="n">
-        <v>7155856</v>
+        <v>7155804</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,16 +1013,16 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833922</t>
+          <t>https://artportalen.se/Sighting/134833920</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136583233</v>
+        <v>134833922</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1050,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730841</v>
+        <v>730864</v>
       </c>
       <c r="R5" t="n">
-        <v>7155872</v>
+        <v>7155856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,17 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,24 +1114,28 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583233</t>
+          <t>https://artportalen.se/Sighting/134833922</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136583235</v>
+        <v>136583233</v>
       </c>
       <c r="B6" t="n">
         <v>92130</v>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730817</v>
+        <v>730841</v>
       </c>
       <c r="R6" t="n">
-        <v>7155898</v>
+        <v>7155872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,51 +1236,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583235</t>
+          <t>https://artportalen.se/Sighting/136583233</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134833918</v>
+        <v>136583235</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730994</v>
+        <v>730817</v>
       </c>
       <c r="R7" t="n">
-        <v>7155941</v>
+        <v>7155898</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,22 +1307,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>19:05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19:05</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,66 +1332,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833918</t>
+          <t>https://artportalen.se/Sighting/136583235</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134833923</v>
+        <v>137454521</v>
       </c>
       <c r="B8" t="n">
-        <v>92102</v>
+        <v>92185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730828</v>
+        <v>730797</v>
       </c>
       <c r="R8" t="n">
-        <v>7155858</v>
+        <v>7156186</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,22 +1414,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>19:36</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>19:36</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,53 +1439,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833923</t>
+          <t>https://artportalen.se/Sighting/137454521</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136583240</v>
+        <v>137454524</v>
       </c>
       <c r="B9" t="n">
-        <v>92144</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730832</v>
+        <v>730883</v>
       </c>
       <c r="R9" t="n">
-        <v>7155854</v>
+        <v>7155940</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,12 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1575,51 +1557,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583240</t>
+          <t>https://artportalen.se/Sighting/137454524</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136583213</v>
+        <v>134833918</v>
       </c>
       <c r="B10" t="n">
-        <v>83356</v>
+        <v>92102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730685</v>
+        <v>730994</v>
       </c>
       <c r="R10" t="n">
-        <v>7156223</v>
+        <v>7155941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,17 +1628,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,62 +1658,66 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583213</t>
+          <t>https://artportalen.se/Sighting/134833918</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136583218</v>
+        <v>134833923</v>
       </c>
       <c r="B11" t="n">
-        <v>83356</v>
+        <v>92102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730834</v>
+        <v>730828</v>
       </c>
       <c r="R11" t="n">
-        <v>7156182</v>
+        <v>7155858</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,17 +1744,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,49 +1774,53 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583218</t>
+          <t>https://artportalen.se/Sighting/134833923</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136583226</v>
+        <v>136583240</v>
       </c>
       <c r="B12" t="n">
-        <v>83356</v>
+        <v>92144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730895</v>
+        <v>730832</v>
       </c>
       <c r="R12" t="n">
-        <v>7156043</v>
+        <v>7155854</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,38 +1896,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583226</t>
+          <t>https://artportalen.se/Sighting/136583240</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136583238</v>
+        <v>137454527</v>
       </c>
       <c r="B13" t="n">
-        <v>83356</v>
+        <v>92196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730834</v>
+        <v>730862</v>
       </c>
       <c r="R13" t="n">
-        <v>7155879</v>
+        <v>7155878</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2003,13 +2003,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583238</t>
+          <t>https://artportalen.se/Sighting/137454527</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136583248</v>
+        <v>136583213</v>
       </c>
       <c r="B14" t="n">
         <v>83356</v>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730984</v>
+        <v>730685</v>
       </c>
       <c r="R14" t="n">
-        <v>7155892</v>
+        <v>7156223</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,13 +2110,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583248</t>
+          <t>https://artportalen.se/Sighting/136583213</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136583249</v>
+        <v>136583218</v>
       </c>
       <c r="B15" t="n">
         <v>83356</v>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730984</v>
+        <v>730834</v>
       </c>
       <c r="R15" t="n">
-        <v>7155878</v>
+        <v>7156182</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2217,13 +2217,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583249</t>
+          <t>https://artportalen.se/Sighting/136583218</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136583250</v>
+        <v>136583226</v>
       </c>
       <c r="B16" t="n">
         <v>83356</v>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>731011</v>
+        <v>730895</v>
       </c>
       <c r="R16" t="n">
-        <v>7155909</v>
+        <v>7156043</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2324,13 +2324,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583250</t>
+          <t>https://artportalen.se/Sighting/136583226</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136583251</v>
+        <v>136583238</v>
       </c>
       <c r="B17" t="n">
         <v>83356</v>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>731012</v>
+        <v>730834</v>
       </c>
       <c r="R17" t="n">
-        <v>7155899</v>
+        <v>7155879</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,13 +2431,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583251</t>
+          <t>https://artportalen.se/Sighting/136583238</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136583252</v>
+        <v>136583248</v>
       </c>
       <c r="B18" t="n">
         <v>83356</v>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>731004</v>
+        <v>730984</v>
       </c>
       <c r="R18" t="n">
-        <v>7155904</v>
+        <v>7155892</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,13 +2538,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583252</t>
+          <t>https://artportalen.se/Sighting/136583248</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136583253</v>
+        <v>136583249</v>
       </c>
       <c r="B19" t="n">
         <v>83356</v>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730985</v>
+        <v>730984</v>
       </c>
       <c r="R19" t="n">
-        <v>7155895</v>
+        <v>7155878</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,13 +2645,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583253</t>
+          <t>https://artportalen.se/Sighting/136583249</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136583254</v>
+        <v>136583250</v>
       </c>
       <c r="B20" t="n">
         <v>83356</v>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>731042</v>
+        <v>731011</v>
       </c>
       <c r="R20" t="n">
-        <v>7155886</v>
+        <v>7155909</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2752,51 +2752,51 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583254</t>
+          <t>https://artportalen.se/Sighting/136583250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134833904</v>
+        <v>136583251</v>
       </c>
       <c r="B21" t="n">
-        <v>96540</v>
+        <v>83356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2812</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730830</v>
+        <v>731012</v>
       </c>
       <c r="R21" t="n">
-        <v>7156167</v>
+        <v>7155899</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,27 +2823,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>18:13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>18:13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,66 +2848,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833904</t>
+          <t>https://artportalen.se/Sighting/136583251</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134833900</v>
+        <v>136583252</v>
       </c>
       <c r="B22" t="n">
-        <v>92051</v>
+        <v>83356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730684</v>
+        <v>731004</v>
       </c>
       <c r="R22" t="n">
-        <v>7156260</v>
+        <v>7155904</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2944,22 +2930,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:53</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:53</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,66 +2955,62 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833900</t>
+          <t>https://artportalen.se/Sighting/136583252</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134833926</v>
+        <v>136583253</v>
       </c>
       <c r="B23" t="n">
-        <v>92051</v>
+        <v>83356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730817</v>
+        <v>730985</v>
       </c>
       <c r="R23" t="n">
-        <v>7155876</v>
+        <v>7155895</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3060,22 +3037,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,53 +3062,49 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833926</t>
+          <t>https://artportalen.se/Sighting/136583253</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136583223</v>
+        <v>136583254</v>
       </c>
       <c r="B24" t="n">
-        <v>92093</v>
+        <v>83356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3146,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730830</v>
+        <v>731042</v>
       </c>
       <c r="R24" t="n">
-        <v>7156196</v>
+        <v>7155886</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3212,16 +3180,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583223</t>
+          <t>https://artportalen.se/Sighting/136583254</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136583225</v>
+        <v>134833904</v>
       </c>
       <c r="B25" t="n">
-        <v>92093</v>
+        <v>96540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3229,34 +3197,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730914</v>
+        <v>730830</v>
       </c>
       <c r="R25" t="n">
-        <v>7156044</v>
+        <v>7156167</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3283,17 +3251,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,27 +3286,31 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583225</t>
+          <t>https://artportalen.se/Sighting/134833904</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136583227</v>
+        <v>134833900</v>
       </c>
       <c r="B26" t="n">
-        <v>92093</v>
+        <v>92051</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3356,14 +3338,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730901</v>
+        <v>730684</v>
       </c>
       <c r="R26" t="n">
-        <v>7156045</v>
+        <v>7156260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3390,17 +3372,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,27 +3402,31 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583227</t>
+          <t>https://artportalen.se/Sighting/134833900</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136583232</v>
+        <v>134833926</v>
       </c>
       <c r="B27" t="n">
-        <v>92093</v>
+        <v>92051</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3463,11 +3454,11 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730844</v>
+        <v>730817</v>
       </c>
       <c r="R27" t="n">
         <v>7155876</v>
@@ -3497,17 +3488,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,24 +3518,28 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583232</t>
+          <t>https://artportalen.se/Sighting/134833926</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136583236</v>
+        <v>136583223</v>
       </c>
       <c r="B28" t="n">
         <v>92093</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730823</v>
+        <v>730830</v>
       </c>
       <c r="R28" t="n">
-        <v>7155886</v>
+        <v>7156196</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3640,13 +3640,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583236</t>
+          <t>https://artportalen.se/Sighting/136583223</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136583239</v>
+        <v>136583225</v>
       </c>
       <c r="B29" t="n">
         <v>92093</v>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730832</v>
+        <v>730914</v>
       </c>
       <c r="R29" t="n">
-        <v>7155864</v>
+        <v>7156044</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3747,13 +3747,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583239</t>
+          <t>https://artportalen.se/Sighting/136583225</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136583243</v>
+        <v>136583227</v>
       </c>
       <c r="B30" t="n">
         <v>92093</v>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730930</v>
+        <v>730901</v>
       </c>
       <c r="R30" t="n">
-        <v>7155880</v>
+        <v>7156045</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3854,38 +3854,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583243</t>
+          <t>https://artportalen.se/Sighting/136583227</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136583220</v>
+        <v>136583232</v>
       </c>
       <c r="B31" t="n">
-        <v>79488</v>
+        <v>92093</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730834</v>
+        <v>730844</v>
       </c>
       <c r="R31" t="n">
-        <v>7156154</v>
+        <v>7155876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3961,38 +3961,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583220</t>
+          <t>https://artportalen.se/Sighting/136583232</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136583229</v>
+        <v>136583236</v>
       </c>
       <c r="B32" t="n">
-        <v>79488</v>
+        <v>92093</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730860</v>
+        <v>730823</v>
       </c>
       <c r="R32" t="n">
-        <v>7155963</v>
+        <v>7155886</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4068,38 +4068,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583229</t>
+          <t>https://artportalen.se/Sighting/136583236</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136583230</v>
+        <v>136583239</v>
       </c>
       <c r="B33" t="n">
-        <v>79488</v>
+        <v>92093</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730856</v>
+        <v>730832</v>
       </c>
       <c r="R33" t="n">
-        <v>7155937</v>
+        <v>7155864</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4175,51 +4175,51 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583230</t>
+          <t>https://artportalen.se/Sighting/136583239</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134833927</v>
+        <v>136583243</v>
       </c>
       <c r="B34" t="n">
-        <v>80575</v>
+        <v>92093</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730771</v>
+        <v>730930</v>
       </c>
       <c r="R34" t="n">
-        <v>7155915</v>
+        <v>7155880</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4246,22 +4246,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>19:42</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>19:42</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4276,66 +4271,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833927</t>
+          <t>https://artportalen.se/Sighting/136583243</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134833928</v>
+        <v>136583220</v>
       </c>
       <c r="B35" t="n">
-        <v>80575</v>
+        <v>79488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730722</v>
+        <v>730834</v>
       </c>
       <c r="R35" t="n">
-        <v>7155984</v>
+        <v>7156154</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4362,22 +4353,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>19:46</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>19:46</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,66 +4378,62 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833928</t>
+          <t>https://artportalen.se/Sighting/136583220</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134833929</v>
+        <v>136583229</v>
       </c>
       <c r="B36" t="n">
-        <v>80575</v>
+        <v>79488</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730710</v>
+        <v>730860</v>
       </c>
       <c r="R36" t="n">
-        <v>7155964</v>
+        <v>7155963</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4478,22 +4460,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4508,53 +4485,49 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833929</t>
+          <t>https://artportalen.se/Sighting/136583229</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136583242</v>
+        <v>136583230</v>
       </c>
       <c r="B37" t="n">
-        <v>80603</v>
+        <v>79488</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4564,10 +4537,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730886</v>
+        <v>730856</v>
       </c>
       <c r="R37" t="n">
-        <v>7155860</v>
+        <v>7155937</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4630,51 +4603,51 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583242</t>
+          <t>https://artportalen.se/Sighting/136583230</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134833930</v>
+        <v>137454526</v>
       </c>
       <c r="B38" t="n">
-        <v>80587</v>
+        <v>79535</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730703</v>
+        <v>730871</v>
       </c>
       <c r="R38" t="n">
-        <v>7155954</v>
+        <v>7155879</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4701,22 +4674,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>19:49</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>19:49</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4731,31 +4699,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833930</t>
+          <t>https://artportalen.se/Sighting/137454526</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134833892</v>
+        <v>134833927</v>
       </c>
       <c r="B39" t="n">
-        <v>57993</v>
+        <v>80575</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4763,38 +4727,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730648</v>
+        <v>730771</v>
       </c>
       <c r="R39" t="n">
-        <v>7156347</v>
+        <v>7155915</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4826,7 +4786,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4836,19 +4796,14 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, men osäkert bild gran</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
@@ -4871,16 +4826,16 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833892</t>
+          <t>https://artportalen.se/Sighting/134833927</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134833894</v>
+        <v>134833928</v>
       </c>
       <c r="B40" t="n">
-        <v>57993</v>
+        <v>80575</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4888,42 +4843,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730680</v>
+        <v>730722</v>
       </c>
       <c r="R40" t="n">
-        <v>7156324</v>
+        <v>7155984</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4955,7 +4902,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4965,19 +4912,14 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -5000,16 +4942,16 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833894</t>
+          <t>https://artportalen.se/Sighting/134833928</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134833896</v>
+        <v>134833929</v>
       </c>
       <c r="B41" t="n">
-        <v>57993</v>
+        <v>80575</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,42 +4959,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730700</v>
+        <v>730710</v>
       </c>
       <c r="R41" t="n">
-        <v>7156310</v>
+        <v>7155964</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5084,7 +5018,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5094,19 +5028,14 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -5129,16 +5058,16 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833896</t>
+          <t>https://artportalen.se/Sighting/134833929</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134833897</v>
+        <v>136583242</v>
       </c>
       <c r="B42" t="n">
-        <v>57993</v>
+        <v>80603</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5146,42 +5075,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730674</v>
+        <v>730886</v>
       </c>
       <c r="R42" t="n">
-        <v>7156298</v>
+        <v>7155860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5208,34 +5129,24 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:43</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:43</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Bohål asp bild</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
@@ -5243,74 +5154,62 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833897</t>
+          <t>https://artportalen.se/Sighting/136583242</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134833903</v>
+        <v>134833930</v>
       </c>
       <c r="B43" t="n">
-        <v>57993</v>
+        <v>80587</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730803</v>
+        <v>730703</v>
       </c>
       <c r="R43" t="n">
-        <v>7156175</v>
+        <v>7155954</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5342,7 +5241,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5352,19 +5251,14 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
@@ -5387,13 +5281,13 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833903</t>
+          <t>https://artportalen.se/Sighting/134833930</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134833910</v>
+        <v>134833892</v>
       </c>
       <c r="B44" t="n">
         <v>57993</v>
@@ -5424,11 +5318,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5436,10 +5326,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730860</v>
+        <v>730648</v>
       </c>
       <c r="R44" t="n">
-        <v>7156153</v>
+        <v>7156347</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5471,7 +5361,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5481,12 +5371,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Skalad gran. Färsk?</t>
+          <t>Äldre ringhack, men osäkert bild gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5516,13 +5406,13 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833910</t>
+          <t>https://artportalen.se/Sighting/134833892</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134833915</v>
+        <v>134833894</v>
       </c>
       <c r="B45" t="n">
         <v>57993</v>
@@ -5565,10 +5455,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730973</v>
+        <v>730680</v>
       </c>
       <c r="R45" t="n">
-        <v>7155960</v>
+        <v>7156324</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5600,7 +5490,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5610,12 +5500,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5645,13 +5535,13 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833915</t>
+          <t>https://artportalen.se/Sighting/134833894</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134833917</v>
+        <v>134833896</v>
       </c>
       <c r="B46" t="n">
         <v>57993</v>
@@ -5694,10 +5584,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730993</v>
+        <v>730700</v>
       </c>
       <c r="R46" t="n">
-        <v>7155936</v>
+        <v>7156310</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5729,7 +5619,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5739,7 +5629,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5774,13 +5664,13 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833917</t>
+          <t>https://artportalen.se/Sighting/134833896</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134833919</v>
+        <v>134833897</v>
       </c>
       <c r="B47" t="n">
         <v>57993</v>
@@ -5813,7 +5703,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5823,10 +5713,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731009</v>
+        <v>730674</v>
       </c>
       <c r="R47" t="n">
-        <v>7155911</v>
+        <v>7156298</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5858,7 +5748,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5868,12 +5758,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Barksprätt färska bild</t>
+          <t>Bohål asp bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5903,13 +5793,13 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833919</t>
+          <t>https://artportalen.se/Sighting/134833897</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134833932</v>
+        <v>134833903</v>
       </c>
       <c r="B48" t="n">
         <v>57993</v>
@@ -5952,10 +5842,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730680</v>
+        <v>730803</v>
       </c>
       <c r="R48" t="n">
-        <v>7156023</v>
+        <v>7156175</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5987,7 +5877,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5997,12 +5887,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Barksprätt äldre</t>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6032,13 +5922,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833932</t>
+          <t>https://artportalen.se/Sighting/134833903</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134833933</v>
+        <v>134833910</v>
       </c>
       <c r="B49" t="n">
         <v>57993</v>
@@ -6071,7 +5961,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6081,10 +5971,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730653</v>
+        <v>730860</v>
       </c>
       <c r="R49" t="n">
-        <v>7156123</v>
+        <v>7156153</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6116,7 +6006,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6126,12 +6016,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Barksprätt äldre</t>
+          <t>Skalad gran. Färsk?</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6161,13 +6051,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833933</t>
+          <t>https://artportalen.se/Sighting/134833910</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134833934</v>
+        <v>134833915</v>
       </c>
       <c r="B50" t="n">
         <v>57993</v>
@@ -6210,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730648</v>
+        <v>730973</v>
       </c>
       <c r="R50" t="n">
-        <v>7156132</v>
+        <v>7155960</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6245,7 +6135,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6255,12 +6145,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Skalad gran äldre</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6290,16 +6180,16 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833934</t>
+          <t>https://artportalen.se/Sighting/134833915</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136583231</v>
+        <v>134833917</v>
       </c>
       <c r="B51" t="n">
-        <v>58008</v>
+        <v>57993</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6325,16 +6215,24 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730836</v>
+        <v>730993</v>
       </c>
       <c r="R51" t="n">
-        <v>7155898</v>
+        <v>7155936</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6361,24 +6259,34 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG51" t="b">
         <v>0</v>
@@ -6386,27 +6294,31 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583231</t>
+          <t>https://artportalen.se/Sighting/134833917</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136583247</v>
+        <v>134833919</v>
       </c>
       <c r="B52" t="n">
-        <v>58008</v>
+        <v>57993</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6432,16 +6344,24 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730987</v>
+        <v>731009</v>
       </c>
       <c r="R52" t="n">
-        <v>7155891</v>
+        <v>7155911</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6468,24 +6388,34 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Barksprätt färska bild</t>
         </is>
       </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG52" t="b">
         <v>0</v>
@@ -6493,62 +6423,74 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583247</t>
+          <t>https://artportalen.se/Sighting/134833919</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134833893</v>
+        <v>134833932</v>
       </c>
       <c r="B53" t="n">
-        <v>99328</v>
+        <v>57993</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730667</v>
+        <v>730680</v>
       </c>
       <c r="R53" t="n">
-        <v>7156336</v>
+        <v>7156023</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6580,7 +6522,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6590,19 +6532,19 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Bild 1</t>
+          <t>Barksprätt äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG53" t="b">
         <v>0</v>
@@ -6625,51 +6567,59 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833893</t>
+          <t>https://artportalen.se/Sighting/134833932</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134833901</v>
+        <v>134833933</v>
       </c>
       <c r="B54" t="n">
-        <v>99328</v>
+        <v>57993</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730736</v>
+        <v>730653</v>
       </c>
       <c r="R54" t="n">
-        <v>7156206</v>
+        <v>7156123</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6701,7 +6651,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6711,14 +6661,19 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Barksprätt äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -6741,51 +6696,59 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833901</t>
+          <t>https://artportalen.se/Sighting/134833933</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134833906</v>
+        <v>134833934</v>
       </c>
       <c r="B55" t="n">
-        <v>99328</v>
+        <v>57993</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730874</v>
+        <v>730648</v>
       </c>
       <c r="R55" t="n">
-        <v>7156177</v>
+        <v>7156132</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6817,7 +6780,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6827,14 +6790,19 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Skalad gran äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG55" t="b">
         <v>0</v>
@@ -6857,51 +6825,51 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833906</t>
+          <t>https://artportalen.se/Sighting/134833934</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134833921</v>
+        <v>136583231</v>
       </c>
       <c r="B56" t="n">
-        <v>99328</v>
+        <v>58008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730857</v>
+        <v>730836</v>
       </c>
       <c r="R56" t="n">
-        <v>7155839</v>
+        <v>7155898</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6928,22 +6896,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>19:32</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>19:32</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6958,53 +6921,49 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833921</t>
+          <t>https://artportalen.se/Sighting/136583231</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136583212</v>
+        <v>136583247</v>
       </c>
       <c r="B57" t="n">
-        <v>99376</v>
+        <v>58008</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7014,10 +6973,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730680</v>
+        <v>730987</v>
       </c>
       <c r="R57" t="n">
-        <v>7156278</v>
+        <v>7155891</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7080,16 +7039,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583212</t>
+          <t>https://artportalen.se/Sighting/136583247</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136583215</v>
+        <v>134833893</v>
       </c>
       <c r="B58" t="n">
-        <v>99376</v>
+        <v>99328</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7117,14 +7076,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730687</v>
+        <v>730667</v>
       </c>
       <c r="R58" t="n">
-        <v>7156223</v>
+        <v>7156336</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7151,17 +7110,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7176,27 +7145,31 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583215</t>
+          <t>https://artportalen.se/Sighting/134833893</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136583216</v>
+        <v>134833901</v>
       </c>
       <c r="B59" t="n">
-        <v>99376</v>
+        <v>99328</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7224,14 +7197,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730680</v>
+        <v>730736</v>
       </c>
       <c r="R59" t="n">
-        <v>7156134</v>
+        <v>7156206</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7258,17 +7231,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7283,27 +7261,31 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583216</t>
+          <t>https://artportalen.se/Sighting/134833901</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136583217</v>
+        <v>134833906</v>
       </c>
       <c r="B60" t="n">
-        <v>99376</v>
+        <v>99328</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7331,14 +7313,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730847</v>
+        <v>730874</v>
       </c>
       <c r="R60" t="n">
-        <v>7156163</v>
+        <v>7156177</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7365,17 +7347,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7390,27 +7377,31 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583217</t>
+          <t>https://artportalen.se/Sighting/134833906</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136583222</v>
+        <v>134833921</v>
       </c>
       <c r="B61" t="n">
-        <v>99376</v>
+        <v>99328</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7438,14 +7429,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ekträsk, Vb</t>
+          <t>Karlebyliden, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730839</v>
+        <v>730857</v>
       </c>
       <c r="R61" t="n">
-        <v>7156155</v>
+        <v>7155839</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7472,17 +7463,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7497,24 +7493,28 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583222</t>
+          <t>https://artportalen.se/Sighting/134833921</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136583224</v>
+        <v>136583212</v>
       </c>
       <c r="B62" t="n">
         <v>99376</v>
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730841</v>
+        <v>730680</v>
       </c>
       <c r="R62" t="n">
-        <v>7156151</v>
+        <v>7156278</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7615,51 +7615,51 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583224</t>
+          <t>https://artportalen.se/Sighting/136583212</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134833895</v>
+        <v>136583215</v>
       </c>
       <c r="B63" t="n">
-        <v>99350</v>
+        <v>99376</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730682</v>
+        <v>730687</v>
       </c>
       <c r="R63" t="n">
-        <v>7156314</v>
+        <v>7156223</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7686,27 +7686,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Bilder</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7721,66 +7711,62 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833895</t>
+          <t>https://artportalen.se/Sighting/136583215</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134833905</v>
+        <v>136583216</v>
       </c>
       <c r="B64" t="n">
-        <v>99350</v>
+        <v>99376</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730821</v>
+        <v>730680</v>
       </c>
       <c r="R64" t="n">
-        <v>7156181</v>
+        <v>7156134</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7807,22 +7793,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7837,66 +7818,62 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833905</t>
+          <t>https://artportalen.se/Sighting/136583216</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134833907</v>
+        <v>136583217</v>
       </c>
       <c r="B65" t="n">
-        <v>99350</v>
+        <v>99376</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>730856</v>
+        <v>730847</v>
       </c>
       <c r="R65" t="n">
-        <v>7156175</v>
+        <v>7156163</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,22 +7900,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>18:25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>18:25</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7953,66 +7925,62 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833907</t>
+          <t>https://artportalen.se/Sighting/136583217</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134833911</v>
+        <v>136583222</v>
       </c>
       <c r="B66" t="n">
-        <v>99350</v>
+        <v>99376</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>730908</v>
+        <v>730839</v>
       </c>
       <c r="R66" t="n">
-        <v>7156134</v>
+        <v>7156155</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8039,22 +8007,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>18:37</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>18:37</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8069,66 +8032,62 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833911</t>
+          <t>https://artportalen.se/Sighting/136583222</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134833912</v>
+        <v>136583224</v>
       </c>
       <c r="B67" t="n">
-        <v>99350</v>
+        <v>99376</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>730904</v>
+        <v>730841</v>
       </c>
       <c r="R67" t="n">
-        <v>7156124</v>
+        <v>7156151</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8155,22 +8114,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>18:40</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>18:40</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8185,69 +8139,69 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833912</t>
+          <t>https://artportalen.se/Sighting/136583224</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134833913</v>
+        <v>137454008</v>
       </c>
       <c r="B68" t="n">
-        <v>99350</v>
+        <v>99434</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>730928</v>
+        <v>730686</v>
       </c>
       <c r="R68" t="n">
-        <v>7156044</v>
+        <v>7156283</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8271,27 +8225,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Bild 2</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8306,69 +8260,69 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833913</t>
+          <t>https://artportalen.se/Sighting/137454008</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134833914</v>
+        <v>137454009</v>
       </c>
       <c r="B69" t="n">
-        <v>99350</v>
+        <v>99434</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>730985</v>
+        <v>730686</v>
       </c>
       <c r="R69" t="n">
-        <v>7155980</v>
+        <v>7156240</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8392,22 +8346,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8422,69 +8381,69 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833914</t>
+          <t>https://artportalen.se/Sighting/137454009</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134833916</v>
+        <v>137454014</v>
       </c>
       <c r="B70" t="n">
-        <v>99350</v>
+        <v>99434</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>730978</v>
+        <v>730846</v>
       </c>
       <c r="R70" t="n">
-        <v>7155952</v>
+        <v>7155852</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8508,22 +8467,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8538,66 +8502,62 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833916</t>
+          <t>https://artportalen.se/Sighting/137454014</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134833925</v>
+        <v>137454520</v>
       </c>
       <c r="B71" t="n">
-        <v>99350</v>
+        <v>99434</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>730823</v>
+        <v>730686</v>
       </c>
       <c r="R71" t="n">
-        <v>7155862</v>
+        <v>7156223</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8624,22 +8584,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8654,66 +8609,62 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833925</t>
+          <t>https://artportalen.se/Sighting/137454520</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134833924</v>
+        <v>137454522</v>
       </c>
       <c r="B72" t="n">
-        <v>98379</v>
+        <v>99434</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>730814</v>
+        <v>730851</v>
       </c>
       <c r="R72" t="n">
-        <v>7155860</v>
+        <v>7156169</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8740,22 +8691,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8770,66 +8716,62 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134833924</t>
+          <t>https://artportalen.se/Sighting/137454522</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134833931</v>
+        <v>137454523</v>
       </c>
       <c r="B73" t="n">
-        <v>98379</v>
+        <v>99434</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Karlebyliden, Vb</t>
+          <t>Ekträsk, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>730697</v>
+        <v>730929</v>
       </c>
       <c r="R73" t="n">
-        <v>7155967</v>
+        <v>7156088</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8856,22 +8798,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>19:50</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>19:50</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8886,20 +8823,1302 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137454523</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134833895</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>730682</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7156314</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Bilder</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
+      <c r="AX74" t="inlineStr">
         <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr">
+      <c r="AY74" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833895</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>134833905</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>730821</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7156181</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833905</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>134833907</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>730856</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7156175</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833907</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>134833911</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>730908</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7156134</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833911</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>134833912</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>730904</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7156124</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833912</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>134833913</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>730928</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7156044</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Bild 2</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833913</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134833914</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>730985</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7155980</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833914</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134833916</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>730978</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7155952</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833916</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>134833925</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99350</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>730823</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7155862</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833925</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>134833924</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98379</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>730814</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7155860</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833924</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134833931</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98379</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Karlebyliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>730697</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7155967</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134833931</t>
         </is>
@@ -8979,6 +10198,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137454525</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137454521</v>
       </c>
       <c r="B8" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137454524</v>
       </c>
       <c r="B9" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>137454527</v>
       </c>
       <c r="B13" t="n">
-        <v>92196</v>
+        <v>92200</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>137454526</v>
       </c>
       <c r="B38" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>137454008</v>
       </c>
       <c r="B68" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>137454009</v>
       </c>
       <c r="B69" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>137454014</v>
       </c>
       <c r="B70" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>137454520</v>
       </c>
       <c r="B71" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>137454522</v>
       </c>
       <c r="B72" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>137454523</v>
       </c>
       <c r="B73" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
